--- a/back/storage/app/ads/2026-09/sept-meta.xlsx
+++ b/back/storage/app/ads/2026-09/sept-meta.xlsx
@@ -1,13 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pulse-kembaliapps\ads-performance\back\storage\app\ads\2026-09\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10178F11-A88C-4761-8BEA-C9447EF6A520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Raw Data Report" r:id="rId3" sheetId="1"/>
+    <sheet name="Raw Data Report" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -113,57 +121,44 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <u val="none"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <u val="none"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <b val="true"/>
-      <u val="none"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor rgb="FFFFFF"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -174,249 +169,37 @@
     <border>
       <left/>
       <right/>
-      <top>
-        <color rgb="000000"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
+      <left style="thin">
+        <color rgb="FF90949C"/>
       </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
+      <right style="thin">
+        <color rgb="FF90949C"/>
       </right>
       <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF90949C"/>
       </top>
       <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="90949C"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF90949C"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="90949C"/>
-      </left>
-      <right style="thin">
-        <color rgb="90949C"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -425,80 +208,360 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="15" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="15" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q16"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultColWidth="12.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="18" max="16384" style="1" width="12.7109375"/>
-    <col min="17" max="17" style="1" width="23.4375" customWidth="true"/>
-    <col min="16" max="16" style="1" width="23.4375" customWidth="true"/>
-    <col min="15" max="15" style="1" width="23.4375" customWidth="true"/>
-    <col min="14" max="14" style="1" width="23.4375" customWidth="true"/>
-    <col min="13" max="13" style="1" width="23.4375" customWidth="true"/>
-    <col min="12" max="12" style="1" width="23.4375" customWidth="true"/>
-    <col min="11" max="11" style="1" width="23.4375" customWidth="true"/>
-    <col min="10" max="10" style="1" width="23.4375" customWidth="true"/>
-    <col min="9" max="9" style="1" width="23.4375" customWidth="true"/>
-    <col min="8" max="8" style="1" width="23.4375" customWidth="true"/>
-    <col min="7" max="7" style="1" width="23.4375" customWidth="true"/>
-    <col min="6" max="6" style="1" width="23.4375" customWidth="true"/>
-    <col min="5" max="5" style="1" width="23.4375" customWidth="true"/>
-    <col min="4" max="4" style="1" width="23.4375" customWidth="true"/>
-    <col min="3" max="3" style="1" width="23.4375" customWidth="true"/>
-    <col min="2" max="2" style="1" width="23.4375" customWidth="true"/>
-    <col min="1" max="1" width="58.59375" style="1" customWidth="true"/>
+    <col min="1" max="1" width="58.6328125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="23.453125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.453125" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="17" width="23.453125" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="12.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -551,7 +614,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
@@ -567,13 +630,13 @@
       <c r="E2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="7" t="n">
-        <v>335.0</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>437.0</v>
-      </c>
-      <c r="H2" s="6" t="n">
+      <c r="F2" s="7">
+        <v>335</v>
+      </c>
+      <c r="G2" s="7">
+        <v>437</v>
+      </c>
+      <c r="H2" s="6">
         <v>1.30447761</v>
       </c>
       <c r="I2" s="6" t="s">
@@ -582,17 +645,17 @@
       <c r="J2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="8" t="n">
-        <v>20858.0</v>
+      <c r="K2" s="8">
+        <v>20858</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="6" t="n">
-        <v>432.0</v>
-      </c>
-      <c r="N2" s="6" t="n">
-        <v>5.0</v>
+      <c r="M2" s="6">
+        <v>432</v>
+      </c>
+      <c r="N2" s="6">
+        <v>5</v>
       </c>
       <c r="O2" s="9" t="s">
         <v>18</v>
@@ -604,7 +667,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
@@ -620,13 +683,13 @@
       <c r="E3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="7" t="n">
-        <v>390.0</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>477.0</v>
-      </c>
-      <c r="H3" s="6" t="n">
+      <c r="F3" s="7">
+        <v>390</v>
+      </c>
+      <c r="G3" s="7">
+        <v>477</v>
+      </c>
+      <c r="H3" s="6">
         <v>1.22307692</v>
       </c>
       <c r="I3" s="6" t="s">
@@ -635,17 +698,17 @@
       <c r="J3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="8" t="n">
-        <v>9934.0</v>
+      <c r="K3" s="8">
+        <v>9934</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="6" t="n">
-        <v>465.0</v>
-      </c>
-      <c r="N3" s="6" t="n">
-        <v>5.0</v>
+      <c r="M3" s="6">
+        <v>465</v>
+      </c>
+      <c r="N3" s="6">
+        <v>5</v>
       </c>
       <c r="O3" s="9" t="s">
         <v>18</v>
@@ -657,7 +720,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
@@ -673,13 +736,13 @@
       <c r="E4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="7" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>42.0</v>
-      </c>
-      <c r="H4" s="6" t="n">
+      <c r="F4" s="7">
+        <v>22</v>
+      </c>
+      <c r="G4" s="7">
+        <v>42</v>
+      </c>
+      <c r="H4" s="6">
         <v>1.90909091</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -688,17 +751,17 @@
       <c r="J4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="8" t="n">
-        <v>2081.0</v>
+      <c r="K4" s="8">
+        <v>2081</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="6" t="n">
-        <v>39.0</v>
-      </c>
-      <c r="N4" s="6" t="n">
-        <v>0.0</v>
+      <c r="M4" s="6">
+        <v>39</v>
+      </c>
+      <c r="N4" s="6">
+        <v>0</v>
       </c>
       <c r="O4" s="9" t="s">
         <v>18</v>
@@ -710,7 +773,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
@@ -726,32 +789,32 @@
       <c r="E5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="7" t="n">
-        <v>359.0</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>476.0</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>1.32590529</v>
+      <c r="F5" s="7">
+        <v>359</v>
+      </c>
+      <c r="G5" s="7">
+        <v>476</v>
+      </c>
+      <c r="H5" s="6">
+        <v>1.3259052899999999</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>22441.0</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>22441.0</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>476.0</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>11.0</v>
+      <c r="J5" s="6">
+        <v>1</v>
+      </c>
+      <c r="K5" s="8">
+        <v>22441</v>
+      </c>
+      <c r="L5" s="8">
+        <v>22441</v>
+      </c>
+      <c r="M5" s="6">
+        <v>476</v>
+      </c>
+      <c r="N5" s="6">
+        <v>11</v>
       </c>
       <c r="O5" s="9" t="s">
         <v>25</v>
@@ -763,7 +826,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
@@ -779,13 +842,13 @@
       <c r="E6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="H6" s="6" t="n">
+      <c r="F6" s="7">
+        <v>2</v>
+      </c>
+      <c r="G6" s="7">
+        <v>5</v>
+      </c>
+      <c r="H6" s="6">
         <v>2.5</v>
       </c>
       <c r="I6" s="6" t="s">
@@ -794,17 +857,17 @@
       <c r="J6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="8" t="n">
-        <v>2719.0</v>
+      <c r="K6" s="8">
+        <v>2719</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M6" s="6" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="N6" s="6" t="n">
-        <v>0.0</v>
+      <c r="M6" s="6">
+        <v>5</v>
+      </c>
+      <c r="N6" s="6">
+        <v>0</v>
       </c>
       <c r="O6" s="9" t="s">
         <v>25</v>
@@ -816,7 +879,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
@@ -832,14 +895,14 @@
       <c r="E7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="7" t="n">
-        <v>29.0</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>60.0</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>2.06896552</v>
+      <c r="F7" s="7">
+        <v>29</v>
+      </c>
+      <c r="G7" s="7">
+        <v>60</v>
+      </c>
+      <c r="H7" s="6">
+        <v>2.0689655199999999</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>22</v>
@@ -847,17 +910,17 @@
       <c r="J7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="8" t="n">
-        <v>2085.0</v>
+      <c r="K7" s="8">
+        <v>2085</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M7" s="6" t="n">
-        <v>56.0</v>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>1.0</v>
+      <c r="M7" s="6">
+        <v>56</v>
+      </c>
+      <c r="N7" s="6">
+        <v>1</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>25</v>
@@ -869,7 +932,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
@@ -885,32 +948,32 @@
       <c r="E8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="7" t="n">
-        <v>638.0</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>839.0</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="F8" s="7">
+        <v>638</v>
+      </c>
+      <c r="G8" s="7">
+        <v>839</v>
+      </c>
+      <c r="H8" s="6">
         <v>1.31504702</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>28007.0</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>28007.0</v>
-      </c>
-      <c r="M8" s="6" t="n">
-        <v>856.0</v>
-      </c>
-      <c r="N8" s="6" t="n">
-        <v>15.0</v>
+      <c r="J8" s="6">
+        <v>1</v>
+      </c>
+      <c r="K8" s="8">
+        <v>867000</v>
+      </c>
+      <c r="L8" s="8">
+        <v>28007</v>
+      </c>
+      <c r="M8" s="6">
+        <v>856</v>
+      </c>
+      <c r="N8" s="6">
+        <v>15</v>
       </c>
       <c r="O8" s="9" t="s">
         <v>27</v>
@@ -922,7 +985,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
@@ -938,32 +1001,32 @@
       <c r="E9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="7" t="n">
-        <v>200.0</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>229.0</v>
-      </c>
-      <c r="H9" s="6" t="n">
+      <c r="F9" s="7">
+        <v>200</v>
+      </c>
+      <c r="G9" s="7">
+        <v>229</v>
+      </c>
+      <c r="H9" s="6">
         <v>1.145</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K9" s="8" t="n">
-        <v>5829.0</v>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>5829.0</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>241.0</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>5.0</v>
+      <c r="J9" s="6">
+        <v>1</v>
+      </c>
+      <c r="K9" s="8">
+        <v>5829</v>
+      </c>
+      <c r="L9" s="8">
+        <v>5829</v>
+      </c>
+      <c r="M9" s="6">
+        <v>241</v>
+      </c>
+      <c r="N9" s="6">
+        <v>5</v>
       </c>
       <c r="O9" s="9" t="s">
         <v>27</v>
@@ -975,7 +1038,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
@@ -991,14 +1054,14 @@
       <c r="E10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="7" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>54.0</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>2.45454545</v>
+      <c r="F10" s="7">
+        <v>22</v>
+      </c>
+      <c r="G10" s="7">
+        <v>54</v>
+      </c>
+      <c r="H10" s="6">
+        <v>2.4545454499999999</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>22</v>
@@ -1006,17 +1069,17 @@
       <c r="J10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K10" s="8" t="n">
-        <v>1843.0</v>
+      <c r="K10" s="8">
+        <v>1843</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M10" s="6" t="n">
-        <v>57.0</v>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>1.0</v>
+      <c r="M10" s="6">
+        <v>57</v>
+      </c>
+      <c r="N10" s="6">
+        <v>1</v>
       </c>
       <c r="O10" s="9" t="s">
         <v>27</v>
@@ -1028,7 +1091,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
@@ -1044,14 +1107,14 @@
       <c r="E11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="7" t="n">
-        <v>660.0</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>799.0</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>1.21060606</v>
+      <c r="F11" s="7">
+        <v>660</v>
+      </c>
+      <c r="G11" s="7">
+        <v>799</v>
+      </c>
+      <c r="H11" s="6">
+        <v>1.2106060599999999</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>22</v>
@@ -1059,17 +1122,17 @@
       <c r="J11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="8" t="n">
-        <v>30238.0</v>
+      <c r="K11" s="8">
+        <v>30238</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="6" t="n">
-        <v>783.0</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>10.0</v>
+      <c r="M11" s="6">
+        <v>783</v>
+      </c>
+      <c r="N11" s="6">
+        <v>10</v>
       </c>
       <c r="O11" s="9" t="s">
         <v>28</v>
@@ -1081,7 +1144,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>17</v>
       </c>
@@ -1097,14 +1160,14 @@
       <c r="E12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="7" t="n">
-        <v>1140.0</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>1255.0</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>1.10087719</v>
+      <c r="F12" s="7">
+        <v>1140</v>
+      </c>
+      <c r="G12" s="7">
+        <v>1255</v>
+      </c>
+      <c r="H12" s="6">
+        <v>1.1008771900000001</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>22</v>
@@ -1112,17 +1175,17 @@
       <c r="J12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K12" s="8" t="n">
-        <v>22481.0</v>
+      <c r="K12" s="8">
+        <v>780456</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M12" s="6" t="n">
-        <v>1236.0</v>
-      </c>
-      <c r="N12" s="6" t="n">
-        <v>11.0</v>
+      <c r="M12" s="6">
+        <v>1236</v>
+      </c>
+      <c r="N12" s="6">
+        <v>11</v>
       </c>
       <c r="O12" s="9" t="s">
         <v>28</v>
@@ -1134,7 +1197,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
@@ -1150,13 +1213,13 @@
       <c r="E13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="7" t="n">
-        <v>182.0</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>208.0</v>
-      </c>
-      <c r="H13" s="6" t="n">
+      <c r="F13" s="7">
+        <v>182</v>
+      </c>
+      <c r="G13" s="7">
+        <v>208</v>
+      </c>
+      <c r="H13" s="6">
         <v>1.14285714</v>
       </c>
       <c r="I13" s="6" t="s">
@@ -1165,17 +1228,17 @@
       <c r="J13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K13" s="8" t="n">
-        <v>6039.0</v>
+      <c r="K13" s="8">
+        <v>6039</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M13" s="6" t="n">
-        <v>199.0</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>1.0</v>
+      <c r="M13" s="6">
+        <v>199</v>
+      </c>
+      <c r="N13" s="6">
+        <v>1</v>
       </c>
       <c r="O13" s="9" t="s">
         <v>28</v>
@@ -1187,7 +1250,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
@@ -1203,32 +1266,32 @@
       <c r="E14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="7" t="n">
-        <v>963.0</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>1354.0</v>
-      </c>
-      <c r="H14" s="6" t="n">
+      <c r="F14" s="7">
+        <v>963</v>
+      </c>
+      <c r="G14" s="7">
+        <v>1354</v>
+      </c>
+      <c r="H14" s="6">
         <v>1.40602285</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>36418.0</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>36418.0</v>
-      </c>
-      <c r="M14" s="6" t="n">
-        <v>1276.0</v>
-      </c>
-      <c r="N14" s="6" t="n">
-        <v>11.0</v>
+      <c r="J14" s="6">
+        <v>1</v>
+      </c>
+      <c r="K14" s="8">
+        <v>36418</v>
+      </c>
+      <c r="L14" s="8">
+        <v>36418</v>
+      </c>
+      <c r="M14" s="6">
+        <v>1276</v>
+      </c>
+      <c r="N14" s="6">
+        <v>11</v>
       </c>
       <c r="O14" s="9" t="s">
         <v>29</v>
@@ -1240,7 +1303,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
@@ -1256,14 +1319,14 @@
       <c r="E15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="7" t="n">
-        <v>530.0</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>797.0</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>1.50377358</v>
+      <c r="F15" s="7">
+        <v>530</v>
+      </c>
+      <c r="G15" s="7">
+        <v>797</v>
+      </c>
+      <c r="H15" s="6">
+        <v>1.5037735800000001</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>22</v>
@@ -1271,17 +1334,17 @@
       <c r="J15" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="8" t="n">
-        <v>26837.0</v>
+      <c r="K15" s="8">
+        <v>26837</v>
       </c>
       <c r="L15" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M15" s="6" t="n">
-        <v>730.0</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>7.0</v>
+      <c r="M15" s="6">
+        <v>730</v>
+      </c>
+      <c r="N15" s="6">
+        <v>7</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>30</v>
@@ -1293,7 +1356,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>17</v>
       </c>
@@ -1309,14 +1372,14 @@
       <c r="E16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="7" t="n">
-        <v>359.0</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>523.0</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>1.45682451</v>
+      <c r="F16" s="7">
+        <v>359</v>
+      </c>
+      <c r="G16" s="7">
+        <v>523</v>
+      </c>
+      <c r="H16" s="6">
+        <v>1.4568245099999999</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>22</v>
@@ -1324,17 +1387,17 @@
       <c r="J16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K16" s="8" t="n">
-        <v>29534.0</v>
+      <c r="K16" s="8">
+        <v>29534</v>
       </c>
       <c r="L16" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M16" s="6" t="n">
-        <v>502.0</v>
-      </c>
-      <c r="N16" s="6" t="n">
-        <v>7.0</v>
+      <c r="M16" s="6">
+        <v>502</v>
+      </c>
+      <c r="N16" s="6">
+        <v>7</v>
       </c>
       <c r="O16" s="9" t="s">
         <v>31</v>
@@ -1347,7 +1410,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>